--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_9.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_24</t>
+          <t>model_23_9_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9993315455010389</v>
+        <v>0.9981308963445745</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7745511707495021</v>
+        <v>0.7386180500678083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9984412777806928</v>
+        <v>0.9950360126594446</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884595151091715</v>
+        <v>0.9989857960890216</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972415884540476</v>
+        <v>0.9977897109506126</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00446995831250332</v>
+        <v>0.00110958067093434</v>
       </c>
       <c r="H2" t="n">
-        <v>1.507577359294485</v>
+        <v>0.1551676165920671</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007564399745899361</v>
+        <v>0.0009226939794633017</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02028731121205688</v>
+        <v>0.0001597432214332913</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01392580861435123</v>
+        <v>0.0005412200635365548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08140487154507348</v>
+        <v>0.00937344763716489</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06685774683986381</v>
+        <v>0.03331036882014878</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000373090883141</v>
+        <v>1.000862663225581</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06970401953745223</v>
+        <v>0.03472846018279187</v>
       </c>
       <c r="P2" t="n">
-        <v>144.8207523929241</v>
+        <v>165.6075462179309</v>
       </c>
       <c r="Q2" t="n">
-        <v>226.4854326590935</v>
+        <v>258.2421089079142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9993356455871942</v>
+        <v>0.9984464347023568</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7745437174120178</v>
+        <v>0.7367635020175511</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9984351103341675</v>
+        <v>0.9954454055953684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9885854342054231</v>
+        <v>0.9988493250310122</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9972605454005018</v>
+        <v>0.9979012179004726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00444254101750294</v>
+        <v>0.0009222634712074356</v>
       </c>
       <c r="H3" t="n">
-        <v>1.507627199796562</v>
+        <v>0.1562685564270042</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007594330050574716</v>
+        <v>0.0008465970091657477</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0200659548377482</v>
+        <v>0.0001812382346183636</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01383010469061256</v>
+        <v>0.0005139160335479477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08203534785892469</v>
+        <v>0.008806543516616402</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06665238943581048</v>
+        <v>0.03036879107253754</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000370802462961</v>
+        <v>1.000717030137374</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06948991964355991</v>
+        <v>0.03166165338055944</v>
       </c>
       <c r="P3" t="n">
-        <v>144.833057530001</v>
+        <v>165.9773592294015</v>
       </c>
       <c r="Q3" t="n">
-        <v>226.4977377961704</v>
+        <v>258.6119219193848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9993400904713282</v>
+        <v>0.9986985014707762</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7745352499305859</v>
+        <v>0.7350751855039079</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9984280925714279</v>
+        <v>0.9957191521920329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9887245765962291</v>
+        <v>0.9987321870725644</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9972813902129152</v>
+        <v>0.9979674390778156</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004412818056832076</v>
+        <v>0.000772625748756292</v>
       </c>
       <c r="H4" t="n">
-        <v>1.507683821883887</v>
+        <v>0.1572708140409787</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007628386896641787</v>
+        <v>0.0007957136528410267</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01982135289842121</v>
+        <v>0.000199688168238234</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0137248698975315</v>
+        <v>0.0004977008558005062</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08274076424222324</v>
+        <v>0.008292365422443125</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06642904528014892</v>
+        <v>0.02779614629325965</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000368321597398</v>
+        <v>1.000600691628873</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0692570672648057</v>
+        <v>0.02897948578691883</v>
       </c>
       <c r="P4" t="n">
-        <v>144.8464835569039</v>
+        <v>166.3314315617566</v>
       </c>
       <c r="Q4" t="n">
-        <v>226.5111638230734</v>
+        <v>258.9659942517399</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.999344883800671</v>
+        <v>0.9988997380711979</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7745256870704783</v>
+        <v>0.7335406006645147</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9984200708351201</v>
+        <v>0.9958907974324865</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9888780801631651</v>
+        <v>0.9986328783222492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9973042572622296</v>
+        <v>0.9980006410099638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004380765041445786</v>
+        <v>0.0006531630097774642</v>
       </c>
       <c r="H5" t="n">
-        <v>1.507747768773458</v>
+        <v>0.1581818098922559</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007667315975433272</v>
+        <v>0.000763808650046965</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01955150508318201</v>
+        <v>0.0002153298942463313</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01360942586497018</v>
+        <v>0.0004895709002040779</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0835252252801208</v>
+        <v>0.007826848049894872</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06618734804663037</v>
+        <v>0.02555705401210132</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000365646250788</v>
+        <v>1.000507813197909</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06900508047967402</v>
+        <v>0.02664507071179159</v>
       </c>
       <c r="P5" t="n">
-        <v>144.8610638056991</v>
+        <v>166.667367655432</v>
       </c>
       <c r="Q5" t="n">
-        <v>226.5257440718685</v>
+        <v>259.3019303454153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9993500396750318</v>
+        <v>0.99906024320234</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7745148074213043</v>
+        <v>0.7321470001027421</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9984109211623351</v>
+        <v>0.9959861523975089</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9890473941058873</v>
+        <v>0.9985491174913904</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9973293452248916</v>
+        <v>0.9980099004526285</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004346287685854668</v>
+        <v>0.0005578802304708389</v>
       </c>
       <c r="H6" t="n">
-        <v>1.507820521037581</v>
+        <v>0.1590091113861338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007711718872647284</v>
+        <v>0.0007460842994187468</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01925386380718368</v>
+        <v>0.0002285227293423836</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01348276957719926</v>
+        <v>0.000487303596681642</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08439522570943225</v>
+        <v>0.007405771262909452</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06592638080354986</v>
+        <v>0.0236194883617499</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000362768553471</v>
+        <v>1.000433733906612</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0687330033207789</v>
+        <v>0.02462501888039088</v>
       </c>
       <c r="P6" t="n">
-        <v>144.8768664075801</v>
+        <v>166.9827325187097</v>
       </c>
       <c r="Q6" t="n">
-        <v>226.5415466737495</v>
+        <v>259.617295208693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.999355564945431</v>
+        <v>0.9991880774595576</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7745024559155829</v>
+        <v>0.7308827131491806</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9984004812366447</v>
+        <v>0.9960245173472692</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9892340777898405</v>
+        <v>0.9984783944002891</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9973568309215112</v>
+        <v>0.9980017163893874</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00430934017725368</v>
+        <v>0.0004819922932341119</v>
       </c>
       <c r="H7" t="n">
-        <v>1.507903115613214</v>
+        <v>0.1597596467361206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007762383301666191</v>
+        <v>0.0007389531152037904</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01892568782234421</v>
+        <v>0.0002396620419401302</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01334400835742471</v>
+        <v>0.0004893075785719603</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0853574010994055</v>
+        <v>0.00702518127052932</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06564556479499342</v>
+        <v>0.02195432288261499</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00035968468162</v>
+        <v>1.000374733480204</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06844023239336894</v>
+        <v>0.02288896385944146</v>
       </c>
       <c r="P7" t="n">
-        <v>144.8939409554211</v>
+        <v>167.2751648663647</v>
       </c>
       <c r="Q7" t="n">
-        <v>226.5586212215906</v>
+        <v>259.9097275563479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9993614485905397</v>
+        <v>0.999289735731573</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7744883743264922</v>
+        <v>0.7297367086324846</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9983884863782531</v>
+        <v>0.9960213940288499</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9894398050929021</v>
+        <v>0.9984187455723348</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9973868770982092</v>
+        <v>0.9979813606895511</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004269996215319955</v>
+        <v>0.0004216435515571073</v>
       </c>
       <c r="H8" t="n">
-        <v>1.507997279264303</v>
+        <v>0.1604399645220487</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007820593740091704</v>
+        <v>0.0007395336700891327</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01856403457627114</v>
+        <v>0.0002490570914257495</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0131923205837483</v>
+        <v>0.0004942919552360708</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08642924505762492</v>
+        <v>0.006681362526399118</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06534520805169998</v>
+        <v>0.02053396093200499</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000356400786676</v>
+        <v>1.000327814277736</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06812708884168932</v>
+        <v>0.02140813416003943</v>
       </c>
       <c r="P8" t="n">
-        <v>144.9122846761678</v>
+        <v>167.54270053083</v>
       </c>
       <c r="Q8" t="n">
-        <v>226.5769649423373</v>
+        <v>260.1772632208132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9993676643631954</v>
+        <v>0.9993703907551222</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7744723467771439</v>
+        <v>0.7286986401846173</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9983747341754085</v>
+        <v>0.9959882406159135</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9896659552000068</v>
+        <v>0.9983682385685178</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9974196451925186</v>
+        <v>0.9979525110306531</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004228431314950397</v>
+        <v>0.0003737632454626363</v>
       </c>
       <c r="H9" t="n">
-        <v>1.508104455560595</v>
+        <v>0.1610562067949249</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007887332481873364</v>
+        <v>0.0007456961464244786</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01816647956477239</v>
+        <v>0.0002570122485764283</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01302689124066154</v>
+        <v>0.0005013561960991023</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08761613856101155</v>
+        <v>0.006370927679853694</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06502638937347203</v>
+        <v>0.01933295749394376</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000352931518216</v>
+        <v>1.000290588882251</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06779469739228357</v>
+        <v>0.02015600151920008</v>
       </c>
       <c r="P9" t="n">
-        <v>144.9318484044687</v>
+        <v>167.7837759890448</v>
       </c>
       <c r="Q9" t="n">
-        <v>226.5965286706382</v>
+        <v>260.4183386790281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9993741714740357</v>
+        <v>0.9994342065514827</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7744539923319775</v>
+        <v>0.7277590131725519</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9983588610796257</v>
+        <v>0.9959337804934161</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9899143691179367</v>
+        <v>0.9983253049090631</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9974552613572668</v>
+        <v>0.9979180403990127</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004184918234798525</v>
+        <v>0.0003358794320441988</v>
       </c>
       <c r="H10" t="n">
-        <v>1.508227191819937</v>
+        <v>0.1616140099790603</v>
       </c>
       <c r="I10" t="n">
-        <v>0.007964363809340312</v>
+        <v>0.0007558190624800077</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0177297864353134</v>
+        <v>0.0002637745583988968</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01284708344708273</v>
+        <v>0.0005097968104394523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08893422602105559</v>
+        <v>0.006090912303281266</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06469094399371927</v>
+        <v>0.01832701372412316</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000349299642399</v>
+        <v>1.000261135437777</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06744497140824708</v>
+        <v>0.01910723264050754</v>
       </c>
       <c r="P10" t="n">
-        <v>144.9525362258282</v>
+        <v>167.9975165911978</v>
       </c>
       <c r="Q10" t="n">
-        <v>226.6172164919977</v>
+        <v>260.6320792811811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9993809334964131</v>
+        <v>0.9994845773230469</v>
       </c>
       <c r="C11" t="n">
-        <v>0.774432940933664</v>
+        <v>0.7269087812420886</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9983405948868136</v>
+        <v>0.9958652906289932</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9901871850982599</v>
+        <v>0.9982885341092613</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9974939812311696</v>
+        <v>0.9978802269728505</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004139700560024454</v>
+        <v>0.0003059771661397023</v>
       </c>
       <c r="H11" t="n">
-        <v>1.508367962617393</v>
+        <v>0.1621187443810904</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008053008715119632</v>
+        <v>0.000768549793084615</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01725019630120766</v>
+        <v>0.0002695661807259623</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01265160661392687</v>
+        <v>0.0005190559545842814</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09039552694697761</v>
+        <v>0.005838227129294837</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06434050481636318</v>
+        <v>0.01749220300990422</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000345525490374</v>
+        <v>1.000237887389363</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06707961330960183</v>
+        <v>0.01823688230588789</v>
       </c>
       <c r="P11" t="n">
-        <v>144.9742636445145</v>
+        <v>168.1840001585093</v>
       </c>
       <c r="Q11" t="n">
-        <v>226.6389439106839</v>
+        <v>260.8185628484925</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9993878370779485</v>
+        <v>0.9995241586867797</v>
       </c>
       <c r="C12" t="n">
-        <v>0.774408787593838</v>
+        <v>0.7261399398690416</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9983194123937852</v>
+        <v>0.9957876430244478</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9904858418926344</v>
+        <v>0.9982567981027184</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9975357976016116</v>
+        <v>0.9978405409387398</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004093536278508926</v>
+        <v>0.0002824799588020398</v>
       </c>
       <c r="H12" t="n">
-        <v>1.508529476112025</v>
+        <v>0.162575161832349</v>
       </c>
       <c r="I12" t="n">
-        <v>0.008155806277697668</v>
+        <v>0.0007829827423083968</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01672517994440895</v>
+        <v>0.000274564792805573</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01244049715400011</v>
+        <v>0.0005287736328711449</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0920209407265971</v>
+        <v>0.005610542246614229</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06398074928061508</v>
+        <v>0.01680714011371476</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000341672328587</v>
+        <v>1.00021961906764</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06670454223590029</v>
+        <v>0.01752265486393195</v>
       </c>
       <c r="P12" t="n">
-        <v>144.99669213344</v>
+        <v>168.3438059043759</v>
       </c>
       <c r="Q12" t="n">
-        <v>226.6613723996094</v>
+        <v>260.9783685943592</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9993947721866314</v>
+        <v>0.9995551452632029</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7743809699997357</v>
+        <v>0.7254451229684544</v>
       </c>
       <c r="D13" t="n">
-        <v>0.998294853095717</v>
+        <v>0.9957049633939377</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9908124027231732</v>
+        <v>0.9982294958863172</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9975808527225131</v>
+        <v>0.9978003709517828</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004047161174813635</v>
+        <v>0.0002640849884868104</v>
       </c>
       <c r="H13" t="n">
-        <v>1.508715492491875</v>
+        <v>0.1629876351590648</v>
       </c>
       <c r="I13" t="n">
-        <v>0.008274991303590027</v>
+        <v>0.0007983510323668205</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01615111037441437</v>
+        <v>0.0002788650562466668</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01221303690003931</v>
+        <v>0.000538609813753984</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09381959529063467</v>
+        <v>0.005405161241930119</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06361730247985713</v>
+        <v>0.01625069193870865</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000337801570252</v>
+        <v>1.000205317570829</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06632562275239549</v>
+        <v>0.01694251753810931</v>
       </c>
       <c r="P13" t="n">
-        <v>145.0194791762612</v>
+        <v>168.4784791610773</v>
       </c>
       <c r="Q13" t="n">
-        <v>226.6841594424306</v>
+        <v>261.1130418510605</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9994015618315393</v>
+        <v>0.9995792714306488</v>
       </c>
       <c r="C14" t="n">
-        <v>0.774348818858681</v>
+        <v>0.7248174689699571</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9982662456261895</v>
+        <v>0.9956202219796635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9911687299927718</v>
+        <v>0.9982057246882817</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9976291483485906</v>
+        <v>0.9977605684616269</v>
       </c>
       <c r="G14" t="n">
-        <v>0.004001758788051079</v>
+        <v>0.0002497626532947238</v>
       </c>
       <c r="H14" t="n">
-        <v>1.50893048732015</v>
+        <v>0.1633602376858138</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008413821899923445</v>
+        <v>0.0008141025618123368</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01552471362591762</v>
+        <v>0.0002826091630386107</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0119692169933785</v>
+        <v>0.0005483560079257742</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09581579577611928</v>
+        <v>0.005220101881469261</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06325945611567554</v>
+        <v>0.0158038809567373</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000334012001001</v>
+        <v>1.000194182416624</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06595254212764659</v>
+        <v>0.0164766848876092</v>
       </c>
       <c r="P14" t="n">
-        <v>145.0420426349758</v>
+        <v>168.5899989557525</v>
       </c>
       <c r="Q14" t="n">
-        <v>226.7067229011452</v>
+        <v>261.2245616457357</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999407980489551</v>
+        <v>0.9995979411653163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7743116092225504</v>
+        <v>0.7242505976996234</v>
       </c>
       <c r="D15" t="n">
-        <v>0.998232891181689</v>
+        <v>0.9955356498401039</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9915565174821626</v>
+        <v>0.9981848579175202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9976806212820536</v>
+        <v>0.9977217708276052</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003958837192371465</v>
+        <v>0.0002386794923055462</v>
       </c>
       <c r="H15" t="n">
-        <v>1.509179308328291</v>
+        <v>0.1636967569594477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008575689324650594</v>
+        <v>0.000829822626882703</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01484301215879255</v>
+        <v>0.0002858958050504088</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01170935648732925</v>
+        <v>0.0005578561490752441</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09802980240664691</v>
+        <v>0.005053421598331543</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06291929109876768</v>
+        <v>0.01544925539647611</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000330429494204</v>
+        <v>1.000185565616008</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06559789558173031</v>
+        <v>0.01610696218307158</v>
       </c>
       <c r="P15" t="n">
-        <v>145.0636098702519</v>
+        <v>168.6807778848105</v>
       </c>
       <c r="Q15" t="n">
-        <v>226.7282901364213</v>
+        <v>261.3153405747937</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9994137214219767</v>
+        <v>0.9996122764725998</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7742684263994749</v>
+        <v>0.7237387764986596</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9981938981465484</v>
+        <v>0.9954526263150925</v>
       </c>
       <c r="E16" t="n">
-        <v>0.991977347218796</v>
+        <v>0.9981666276606642</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9977351544024526</v>
+        <v>0.9976843904409887</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003920447550806352</v>
+        <v>0.000230169434649099</v>
       </c>
       <c r="H16" t="n">
-        <v>1.509468072065035</v>
+        <v>0.1640005961338646</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00876492054330894</v>
+        <v>0.0008452548392205638</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01410322488684223</v>
+        <v>0.0002887671802504169</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01143404666311674</v>
+        <v>0.0005670092574549625</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1004831485907988</v>
+        <v>0.004903243450908607</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06261347738950737</v>
+        <v>0.01517133595465802</v>
       </c>
       <c r="N16" t="n">
-        <v>1.00032722525285</v>
+        <v>1.000178949320339</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06527906274974514</v>
+        <v>0.01581721113524273</v>
       </c>
       <c r="P16" t="n">
-        <v>145.0830989211454</v>
+        <v>168.7533896957272</v>
       </c>
       <c r="Q16" t="n">
-        <v>226.7477791873149</v>
+        <v>261.3879523857105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9994183871407681</v>
+        <v>0.9996231798037345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7742181494014546</v>
+        <v>0.7232767689501578</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9981481829154681</v>
+        <v>0.9953724581752286</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9924325697281222</v>
+        <v>0.9981504510419532</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9977924413047647</v>
+        <v>0.9976487518821221</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00388924786776442</v>
+        <v>0.0002236967462880998</v>
       </c>
       <c r="H17" t="n">
-        <v>1.509804274582301</v>
+        <v>0.1642748637723421</v>
       </c>
       <c r="I17" t="n">
-        <v>0.008986774237368957</v>
+        <v>0.0008601562994625743</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01330297768711032</v>
+        <v>0.0002913150950798035</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01114483440293832</v>
+        <v>0.000575735855046115</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1031990568613855</v>
+        <v>0.004767875410624412</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06236383461401664</v>
+        <v>0.01495649512045184</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000324621130734</v>
+        <v>1.000173917013661</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06501879216446999</v>
+        <v>0.01559322408194257</v>
       </c>
       <c r="P17" t="n">
-        <v>145.0990789804709</v>
+        <v>168.8104384691068</v>
       </c>
       <c r="Q17" t="n">
-        <v>226.7637592466403</v>
+        <v>261.4450011590901</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9994214394767625</v>
+        <v>0.9996313766952107</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7741594281029895</v>
+        <v>0.722859917595051</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9980944230504532</v>
+        <v>0.9952959249163555</v>
       </c>
       <c r="E18" t="n">
-        <v>0.992922934744171</v>
+        <v>0.9981362091713203</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9978519754151617</v>
+        <v>0.9976151236500319</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003868836882914922</v>
+        <v>0.0002188307174205352</v>
       </c>
       <c r="H18" t="n">
-        <v>1.510196944175523</v>
+        <v>0.1645223247437745</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00924766813124046</v>
+        <v>0.0008743821168037934</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01244095258312246</v>
+        <v>0.0002935582754397878</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01084427713887458</v>
+        <v>0.0005839701961217905</v>
       </c>
       <c r="L18" t="n">
-        <v>0.106210624942156</v>
+        <v>0.004646045544568647</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06219997494304095</v>
+        <v>0.01479292795292856</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000322917501342</v>
+        <v>1.00017013383298</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06484795664806459</v>
+        <v>0.01542269352146711</v>
       </c>
       <c r="P18" t="n">
-        <v>145.1096027283284</v>
+        <v>168.8544242137312</v>
       </c>
       <c r="Q18" t="n">
-        <v>226.7742829944978</v>
+        <v>261.4889869037145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9994222228194958</v>
+        <v>0.9996374379973947</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7740906893611395</v>
+        <v>0.722483903098039</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9980310902713334</v>
+        <v>0.9952233595397012</v>
       </c>
       <c r="E19" t="n">
-        <v>0.993448872833846</v>
+        <v>0.9981235784751278</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9979130962857401</v>
+        <v>0.9975835260581952</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003863598666451191</v>
+        <v>0.0002152324666095443</v>
       </c>
       <c r="H19" t="n">
-        <v>1.510656600458788</v>
+        <v>0.1647455431921812</v>
       </c>
       <c r="I19" t="n">
-        <v>0.009555018890950314</v>
+        <v>0.0008878703937801305</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01151639267039367</v>
+        <v>0.0002955476861262469</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0105357091344856</v>
+        <v>0.0005917073066441517</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1095450339036606</v>
+        <v>0.004536303526955437</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06215785281403462</v>
+        <v>0.01467080320260429</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000322480286793</v>
+        <v>1.000167336308895</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06480404129282162</v>
+        <v>0.01529536966768845</v>
       </c>
       <c r="P19" t="n">
-        <v>145.1123124656325</v>
+        <v>168.8875837478224</v>
       </c>
       <c r="Q19" t="n">
-        <v>226.7769927318019</v>
+        <v>261.5221464378057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9994198550133453</v>
+        <v>0.9996418291667933</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7740099895790034</v>
+        <v>0.7221448412491214</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9979562690976523</v>
+        <v>0.9951550695273307</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9940097291297659</v>
+        <v>0.9981124152037272</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9979747827570506</v>
+        <v>0.9975540089879571</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003879432197082111</v>
+        <v>0.0002126256787658644</v>
       </c>
       <c r="H20" t="n">
-        <v>1.51119624027352</v>
+        <v>0.164946824952408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.009918122245845951</v>
+        <v>0.0009005639763678471</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01053044915690997</v>
+        <v>0.0002973059685741407</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01022428570137796</v>
+        <v>0.0005989349724709939</v>
       </c>
       <c r="L20" t="n">
-        <v>0.113232153222222</v>
+        <v>0.004437420358422184</v>
       </c>
       <c r="M20" t="n">
-        <v>0.06228508807958861</v>
+        <v>0.01458168984603171</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000323801853017</v>
+        <v>1.000165309615326</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06493669322704355</v>
+        <v>0.0152024625710365</v>
       </c>
       <c r="P20" t="n">
-        <v>145.1041329540281</v>
+        <v>168.9119546298778</v>
       </c>
       <c r="Q20" t="n">
-        <v>226.7688132201975</v>
+        <v>261.546517319861</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9994132306308349</v>
+        <v>0.999644923765951</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7739149278905781</v>
+        <v>0.7218391237447532</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9978676514303255</v>
+        <v>0.9950913291198232</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9946037292825198</v>
+        <v>0.9981023954022189</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9980356079840764</v>
+        <v>0.9975265935738796</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00392372947343197</v>
+        <v>0.0002107885910261158</v>
       </c>
       <c r="H21" t="n">
-        <v>1.511831918221738</v>
+        <v>0.1651283120693094</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01034817928353101</v>
+        <v>0.00091241188939034</v>
       </c>
       <c r="J21" t="n">
-        <v>0.009486241216522273</v>
+        <v>0.0002988841476303821</v>
       </c>
       <c r="K21" t="n">
-        <v>0.009917210250026643</v>
+        <v>0.0006056480185103611</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1173121714056732</v>
+        <v>0.004348438958868387</v>
       </c>
       <c r="M21" t="n">
-        <v>0.06263967970409787</v>
+        <v>0.01451856022565997</v>
       </c>
       <c r="N21" t="n">
-        <v>1.00032749918279</v>
+        <v>1.000163881338792</v>
       </c>
       <c r="O21" t="n">
-        <v>0.06530638055111401</v>
+        <v>0.0151366453920292</v>
       </c>
       <c r="P21" t="n">
-        <v>145.0814253623734</v>
+        <v>168.9293097300575</v>
       </c>
       <c r="Q21" t="n">
-        <v>226.7461056285428</v>
+        <v>261.5638724200407</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9994009399794852</v>
+        <v>0.9996470064509175</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7738027118106662</v>
+        <v>0.7215635763133188</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9977624921251376</v>
+        <v>0.995031974382754</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9952276690000256</v>
+        <v>0.998093445086461</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9980936953413058</v>
+        <v>0.9975011867207881</v>
       </c>
       <c r="G22" t="n">
-        <v>0.004005917115600518</v>
+        <v>0.0002095522192627178</v>
       </c>
       <c r="H22" t="n">
-        <v>1.512582307664817</v>
+        <v>0.1652918889276382</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01085851204942725</v>
+        <v>0.0009234446045826268</v>
       </c>
       <c r="J22" t="n">
-        <v>0.008389401755585897</v>
+        <v>0.0003002938762426782</v>
       </c>
       <c r="K22" t="n">
-        <v>0.009623956902506572</v>
+        <v>0.0006118692404126525</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1218274643443203</v>
+        <v>0.004268405244339562</v>
       </c>
       <c r="M22" t="n">
-        <v>0.06329231482257951</v>
+        <v>0.01447591859823472</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000334359081217</v>
+        <v>1.000162920099577</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06598679969773037</v>
+        <v>0.01509218842224412</v>
       </c>
       <c r="P22" t="n">
-        <v>145.0399654640347</v>
+        <v>168.9410751860748</v>
       </c>
       <c r="Q22" t="n">
-        <v>226.7046457302041</v>
+        <v>261.5756378760581</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9993812048656913</v>
+        <v>0.9996483197167726</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7736697643691244</v>
+        <v>0.7213150990371204</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9976374588491779</v>
+        <v>0.994977012324088</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9958763402170723</v>
+        <v>0.998085522497806</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9981465364509385</v>
+        <v>0.9974777706713892</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004137885912411796</v>
+        <v>0.0002087726079210318</v>
       </c>
       <c r="H23" t="n">
-        <v>1.513471327818574</v>
+        <v>0.165439395772449</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01146529218586428</v>
+        <v>0.0009336608193210773</v>
       </c>
       <c r="J23" t="n">
-        <v>0.007249086164081675</v>
+        <v>0.0003015417316494078</v>
       </c>
       <c r="K23" t="n">
-        <v>0.009357189174972979</v>
+        <v>0.0006176029862984965</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1268160530073051</v>
+        <v>0.004196187550736304</v>
       </c>
       <c r="M23" t="n">
-        <v>0.06432640136376196</v>
+        <v>0.01444896563498688</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000345374028451</v>
+        <v>1.000162313976874</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06706490944382519</v>
+        <v>0.01506408801555049</v>
       </c>
       <c r="P23" t="n">
-        <v>144.975140541493</v>
+        <v>168.9485297973587</v>
       </c>
       <c r="Q23" t="n">
-        <v>226.6398208076624</v>
+        <v>261.583092487342</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.99935177447111</v>
+        <v>0.999649055357451</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7735119312767975</v>
+        <v>0.721091150687694</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9974885283784908</v>
+        <v>0.9949265976396252</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9965417943048107</v>
+        <v>0.9980783366536313</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9981908052510604</v>
+        <v>0.9974563315156034</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004334687096491419</v>
+        <v>0.0002083358998363117</v>
       </c>
       <c r="H24" t="n">
-        <v>1.514526758433719</v>
+        <v>0.1655723411867335</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01218804419431556</v>
+        <v>0.0009430317791239466</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006079267538348252</v>
+        <v>0.0003026735453653177</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009133698652324511</v>
+        <v>0.0006228526622446321</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1323242846532543</v>
+        <v>0.004131190935383996</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06583834062680666</v>
+        <v>0.01443384563573796</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000361800295194</v>
+        <v>1.000161974450407</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06864121509144344</v>
+        <v>0.01504832432663083</v>
       </c>
       <c r="P24" t="n">
-        <v>144.8822117041899</v>
+        <v>168.9527177555151</v>
       </c>
       <c r="Q24" t="n">
-        <v>226.5468919703593</v>
+        <v>261.5872804454984</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9993098143027509</v>
+        <v>0.9996493314618929</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7733239707391368</v>
+        <v>0.7208892088820329</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9973107534865769</v>
+        <v>0.9948799339258234</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9972127896199331</v>
+        <v>0.998071868938454</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9982221921454389</v>
+        <v>0.9974365407481439</v>
       </c>
       <c r="G25" t="n">
-        <v>0.004615274935517404</v>
+        <v>0.0002081719923124459</v>
       </c>
       <c r="H25" t="n">
-        <v>1.515783651414534</v>
+        <v>0.1656922225660057</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01305077671365954</v>
+        <v>0.0009517055175584928</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004899707848396386</v>
+        <v>0.0003036922494410497</v>
       </c>
       <c r="K25" t="n">
-        <v>0.008975242281027964</v>
+        <v>0.0006276987073466572</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1384024126143134</v>
+        <v>0.004072738659374866</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0679358148219141</v>
+        <v>0.01442816663032576</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000385219924046</v>
+        <v>1.000161847017588</v>
       </c>
       <c r="O25" t="n">
-        <v>0.07082798310540676</v>
+        <v>0.01504240355420108</v>
       </c>
       <c r="P25" t="n">
-        <v>144.7567676769503</v>
+        <v>168.9542918676548</v>
       </c>
       <c r="Q25" t="n">
-        <v>226.4214479431198</v>
+        <v>261.5888545576381</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_0</t>
+          <t>model_23_9_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9992517668494691</v>
+        <v>0.9996492750404057</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7730995443724014</v>
+        <v>0.7207075030888332</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9970982242860345</v>
+        <v>0.9948370405278927</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9978737493734591</v>
+        <v>0.9980660449912502</v>
       </c>
       <c r="F26" t="n">
-        <v>0.998235117528105</v>
+        <v>0.997418386624202</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005003438522896957</v>
+        <v>0.0002082054865445791</v>
       </c>
       <c r="H26" t="n">
-        <v>1.517284391562283</v>
+        <v>0.1658000909741306</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01408217012723032</v>
+        <v>0.0009596784387837347</v>
       </c>
       <c r="J26" t="n">
-        <v>0.003737789926812115</v>
+        <v>0.0003046095561855118</v>
       </c>
       <c r="K26" t="n">
-        <v>0.008909988636937396</v>
+        <v>0.0006321439974846233</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1451073581368066</v>
+        <v>0.004020090200835611</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07073498796845135</v>
+        <v>0.01442932730741732</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000417618502622</v>
+        <v>1.000161873058274</v>
       </c>
       <c r="O26" t="n">
-        <v>0.07374632284787933</v>
+        <v>0.01504361364371935</v>
       </c>
       <c r="P26" t="n">
-        <v>144.5952597966582</v>
+        <v>168.9539700997024</v>
       </c>
       <c r="Q26" t="n">
-        <v>226.2599400628276</v>
+        <v>261.5885327896856</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_9.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9981308963445745</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7386180500678083</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9950360126594446</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9989857960890216</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9977897109506126</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00110958067093434</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1551676165920671</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009226939794633017</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001597432214332913</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005412200635365548</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00937344763716489</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03331036882014878</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000862663225581</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03472846018279187</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P2" t="n">
-        <v>165.6075462179309</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q2" t="n">
-        <v>258.2421089079142</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9984464347023568</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7367635020175511</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9954454055953684</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9988493250310122</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9979012179004726</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009222634712074356</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1562685564270042</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008465970091657477</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001812382346183636</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005139160335479477</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008806543516616402</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03036879107253754</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000717030137374</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03166165338055944</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P3" t="n">
-        <v>165.9773592294015</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q3" t="n">
-        <v>258.6119219193848</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9986985014707762</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7350751855039079</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9957191521920329</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9987321870725644</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9979674390778156</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000772625748756292</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1572708140409787</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007957136528410267</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000199688168238234</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0004977008558005062</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008292365422443125</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02779614629325965</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000600691628873</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02897948578691883</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P4" t="n">
-        <v>166.3314315617566</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q4" t="n">
-        <v>258.9659942517399</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9988997380711979</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7335406006645147</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9958907974324865</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9986328783222492</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9980006410099638</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006531630097774642</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1581818098922559</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000763808650046965</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002153298942463313</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004895709002040779</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007826848049894872</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02555705401210132</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000507813197909</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02664507071179159</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P5" t="n">
-        <v>166.667367655432</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q5" t="n">
-        <v>259.3019303454153</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.99906024320234</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7321470001027421</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9959861523975089</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9985491174913904</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9980099004526285</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005578802304708389</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1590091113861338</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007460842994187468</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002285227293423836</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000487303596681642</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007405771262909452</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0236194883617499</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000433733906612</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02462501888039088</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P6" t="n">
-        <v>166.9827325187097</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q6" t="n">
-        <v>259.617295208693</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9991880774595576</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7308827131491806</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9960245173472692</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9984783944002891</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9980017163893874</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0004819922932341119</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1597596467361206</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007389531152037904</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002396620419401302</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004893075785719603</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00702518127052932</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02195432288261499</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000374733480204</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02288896385944146</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P7" t="n">
-        <v>167.2751648663647</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q7" t="n">
-        <v>259.9097275563479</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.999289735731573</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7297367086324846</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9960213940288499</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9984187455723348</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9979813606895511</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004216435515571073</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1604399645220487</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0007395336700891327</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002490570914257495</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004942919552360708</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006681362526399118</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02053396093200499</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000327814277736</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02140813416003943</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P8" t="n">
-        <v>167.54270053083</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q8" t="n">
-        <v>260.1772632208132</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9993703907551222</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7286986401846173</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9959882406159135</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9983682385685178</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9979525110306531</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003737632454626363</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1610562067949249</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007456961464244786</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002570122485764283</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0005013561960991023</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006370927679853694</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01933295749394376</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000290588882251</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02015600151920008</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P9" t="n">
-        <v>167.7837759890448</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q9" t="n">
-        <v>260.4183386790281</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9994342065514827</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7277590131725519</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9959337804934161</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9983253049090631</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9979180403990127</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003358794320441988</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1616140099790603</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007558190624800077</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002637745583988968</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0005097968104394523</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006090912303281266</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01832701372412316</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000261135437777</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01910723264050754</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P10" t="n">
-        <v>167.9975165911978</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q10" t="n">
-        <v>260.6320792811811</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9994845773230469</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7269087812420886</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9958652906289932</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9982885341092613</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9978802269728505</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003059771661397023</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1621187443810904</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000768549793084615</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002695661807259623</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0005190559545842814</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005838227129294837</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01749220300990422</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000237887389363</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01823688230588789</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P11" t="n">
-        <v>168.1840001585093</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q11" t="n">
-        <v>260.8185628484925</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9995241586867797</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7261399398690416</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9957876430244478</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9982567981027184</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9978405409387398</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002824799588020398</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.162575161832349</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0007829827423083968</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000274564792805573</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0005287736328711449</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005610542246614229</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01680714011371476</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00021961906764</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01752265486393195</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P12" t="n">
-        <v>168.3438059043759</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q12" t="n">
-        <v>260.9783685943592</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9995551452632029</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7254451229684544</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9957049633939377</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9982294958863172</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9978003709517828</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002640849884868104</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1629876351590648</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0007983510323668205</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002788650562466668</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000538609813753984</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005405161241930119</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01625069193870865</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000205317570829</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01694251753810931</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P13" t="n">
-        <v>168.4784791610773</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q13" t="n">
-        <v>261.1130418510605</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9995792714306488</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7248174689699571</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9956202219796635</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9982057246882817</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9977605684616269</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002497626532947238</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1633602376858138</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0008141025618123368</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002826091630386107</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005483560079257742</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005220101881469261</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0158038809567373</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000194182416624</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0164766848876092</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P14" t="n">
-        <v>168.5899989557525</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q14" t="n">
-        <v>261.2245616457357</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9995979411653163</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7242505976996234</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9955356498401039</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9981848579175202</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9977217708276052</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002386794923055462</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1636967569594477</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I15" t="n">
-        <v>0.000829822626882703</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0002858958050504088</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0005578561490752441</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005053421598331543</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01544925539647611</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000185565616008</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01610696218307158</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P15" t="n">
-        <v>168.6807778848105</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q15" t="n">
-        <v>261.3153405747937</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9996122764725998</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7237387764986596</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9954526263150925</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9981666276606642</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9976843904409887</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000230169434649099</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1640005961338646</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0008452548392205638</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002887671802504169</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005670092574549625</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004903243450908607</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01517133595465802</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000178949320339</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01581721113524273</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P16" t="n">
-        <v>168.7533896957272</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q16" t="n">
-        <v>261.3879523857105</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9996231798037345</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7232767689501578</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9953724581752286</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9981504510419532</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9976487518821221</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002236967462880998</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1642748637723421</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0008601562994625743</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0002913150950798035</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000575735855046115</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004767875410624412</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01495649512045184</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000173917013661</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01559322408194257</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P17" t="n">
-        <v>168.8104384691068</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q17" t="n">
-        <v>261.4450011590901</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9996313766952107</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C18" t="n">
-        <v>0.722859917595051</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9952959249163555</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9981362091713203</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9976151236500319</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002188307174205352</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1645223247437745</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0008743821168037934</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0002935582754397878</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0005839701961217905</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004646045544568647</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01479292795292856</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N18" t="n">
-        <v>1.00017013383298</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01542269352146711</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P18" t="n">
-        <v>168.8544242137312</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q18" t="n">
-        <v>261.4889869037145</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9996374379973947</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C19" t="n">
-        <v>0.722483903098039</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9952233595397012</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9981235784751278</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9975835260581952</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0002152324666095443</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1647455431921812</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0008878703937801305</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0002955476861262469</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0005917073066441517</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004536303526955437</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01467080320260429</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000167336308895</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01529536966768845</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P19" t="n">
-        <v>168.8875837478224</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q19" t="n">
-        <v>261.5221464378057</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9996418291667933</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7221448412491214</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9951550695273307</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9981124152037272</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9975540089879571</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002126256787658644</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>0.164946824952408</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0009005639763678471</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0002973059685741407</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0005989349724709939</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004437420358422184</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01458168984603171</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000165309615326</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0152024625710365</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P20" t="n">
-        <v>168.9119546298778</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q20" t="n">
-        <v>261.546517319861</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.999644923765951</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7218391237447532</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9950913291198232</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9981023954022189</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9975265935738796</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0002107885910261158</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1651283120693094</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00091241188939034</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0002988841476303821</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0006056480185103611</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004348438958868387</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01451856022565997</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000163881338792</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0151366453920292</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P21" t="n">
-        <v>168.9293097300575</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q21" t="n">
-        <v>261.5638724200407</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9996470064509175</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7215635763133188</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D22" t="n">
-        <v>0.995031974382754</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E22" t="n">
-        <v>0.998093445086461</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9975011867207881</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002095522192627178</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1652918889276382</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0009234446045826268</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0003002938762426782</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0006118692404126525</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004268405244339562</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01447591859823472</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000162920099577</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01509218842224412</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P22" t="n">
-        <v>168.9410751860748</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q22" t="n">
-        <v>261.5756378760581</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9996483197167726</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7213150990371204</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D23" t="n">
-        <v>0.994977012324088</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E23" t="n">
-        <v>0.998085522497806</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9974777706713892</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002087726079210318</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>0.165439395772449</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0009336608193210773</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0003015417316494078</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0006176029862984965</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004196187550736304</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01444896563498688</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000162313976874</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01506408801555049</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P23" t="n">
-        <v>168.9485297973587</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q23" t="n">
-        <v>261.583092487342</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.999649055357451</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C24" t="n">
-        <v>0.721091150687694</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9949265976396252</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9980783366536313</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9974563315156034</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002083358998363117</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1655723411867335</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0009430317791239466</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0003026735453653177</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0006228526622446321</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004131190935383996</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01443384563573796</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000161974450407</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01504832432663083</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P24" t="n">
-        <v>168.9527177555151</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q24" t="n">
-        <v>261.5872804454984</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9996493314618929</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7208892088820329</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9948799339258234</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E25" t="n">
-        <v>0.998071868938454</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9974365407481439</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002081719923124459</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1656922225660057</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0009517055175584928</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0003036922494410497</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0006276987073466572</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004072738659374866</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01442816663032576</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000161847017588</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O25" t="n">
-        <v>0.01504240355420108</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P25" t="n">
-        <v>168.9542918676548</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q25" t="n">
-        <v>261.5888545576381</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9996492750404057</v>
+        <v>0.9999884752544436</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7207075030888332</v>
+        <v>0.708987424988373</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9948370405278927</v>
+        <v>0.9999770536509758</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9980660449912502</v>
+        <v>0.9999940018213999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.997418386624202</v>
+        <v>0.9999882713929703</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002082054865445791</v>
+        <v>6.841586805405771e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1658000909741306</v>
+        <v>0.1727576356155761</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0009596784387837347</v>
+        <v>7.492446289837229e-06</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0003046095561855118</v>
+        <v>3.235477898143575e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0006321439974846233</v>
+        <v>5.364176528016398e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004020090200835611</v>
+        <v>0.0008455059525182328</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01442932730741732</v>
+        <v>0.002615642713637658</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000161873058274</v>
+        <v>1.000005319113334</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01504361364371935</v>
+        <v>0.002726996039084066</v>
       </c>
       <c r="P26" t="n">
-        <v>168.9539700997024</v>
+        <v>175.7849817282814</v>
       </c>
       <c r="Q26" t="n">
-        <v>261.5885327896856</v>
+        <v>268.4195444182647</v>
       </c>
     </row>
   </sheetData>
